--- a/artfynd/A 58760-2020 artfynd.xlsx
+++ b/artfynd/A 58760-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58760-2020 artfynd.xlsx
+++ b/artfynd/A 58760-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,6 +912,218 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123528619</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90931</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>480986</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6597134</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123528563</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90980</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>480883</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6597075</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58760-2020 artfynd.xlsx
+++ b/artfynd/A 58760-2020 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>123528619</v>
       </c>
       <c r="B4" t="n">
-        <v>90931</v>
+        <v>90948</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>123528563</v>
       </c>
       <c r="B5" t="n">
-        <v>90980</v>
+        <v>90997</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 58760-2020 artfynd.xlsx
+++ b/artfynd/A 58760-2020 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>123528619</v>
       </c>
       <c r="B4" t="n">
-        <v>90948</v>
+        <v>90953</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>123528563</v>
       </c>
       <c r="B5" t="n">
-        <v>90997</v>
+        <v>91002</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 58760-2020 artfynd.xlsx
+++ b/artfynd/A 58760-2020 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>123528619</v>
       </c>
       <c r="B4" t="n">
-        <v>90953</v>
+        <v>90955</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>123528563</v>
       </c>
       <c r="B5" t="n">
-        <v>91002</v>
+        <v>91004</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 58760-2020 artfynd.xlsx
+++ b/artfynd/A 58760-2020 artfynd.xlsx
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123528619</v>
+        <v>123528563</v>
       </c>
       <c r="B4" t="n">
-        <v>90955</v>
+        <v>91004</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,25 +926,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480986</v>
+        <v>480883</v>
       </c>
       <c r="R4" t="n">
-        <v>6597134</v>
+        <v>6597075</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528563</v>
+        <v>123528619</v>
       </c>
       <c r="B5" t="n">
-        <v>91004</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480883</v>
+        <v>480986</v>
       </c>
       <c r="R5" t="n">
-        <v>6597075</v>
+        <v>6597134</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
